--- a/modulo-06-facturacion-electronica-cfdi/clase-01-cfdi-fundamentos-complementos/analisis-pagos-cfdi.xlsx
+++ b/modulo-06-facturacion-electronica-cfdi/clase-01-cfdi-fundamentos-complementos/analisis-pagos-cfdi.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Análisis de Pagos" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Inventario CFDI" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Papel de Trabajo IVA" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t xml:space="preserve">Análisis de pagos — Factura PPD liquidada en parcialidades</t>
   </si>
@@ -191,6 +192,30 @@
     <t xml:space="preserve">Notas</t>
   </si>
   <si>
+    <t xml:space="preserve">cfdi-40-ppd-origen-clase.xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I · Ingreso (PPD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factura de origen. Se liquida en 2 parcialidades documentadas con REP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cfdi-40-rep-ejemplo-clase.xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P · Pago (REP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcialidad 1 de F-2026000. IVA acreditable/causado en marzo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cfdi-40-rep2-ejemplo-clase.xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcialidad 2 (liquida) de F-2026000. IVA en abril.</t>
+  </si>
+  <si>
     <t xml:space="preserve">cfdi-40-ejemplo-clase.xml</t>
   </si>
   <si>
@@ -206,34 +231,110 @@
     <t xml:space="preserve">2026-01-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Factura independiente. No forma parte de la cadena de pagos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cfdi-40-rep-ejemplo-clase.xml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P · Pago (REP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcialidad 1 de la factura F-2026000.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cfdi-40-rep2-ejemplo-clase.xml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcialidad 2 (liquida) de la factura F-2026000.</t>
+    <t xml:space="preserve">Factura independiente, pago en una exhibición. No genera REP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cadena de pagos (sombreada) son tres CFDI ligados por el UUID de F-2026000. La factura PUE es un documento aparte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papel de trabajo — IVA por flujo de efectivo (operación PPD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El IVA se causa conforme se cobra; en una factura PPD, cada REP ubica el IVA en su periodo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emisor (cobra y traslada IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESCUELA KEMPER URGATE SA DE CV · EKU9003173C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receptor (paga y acredita IVA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSIDAD ROBOTICA ESPAÑOLA SC · URE180429TM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factura de origen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-2026000 · PPD · emitida 2026-02-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total de la factura (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base gravada 16% (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA trasladado 16% (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRINCIPIO (FLUJO DE EFECTIVO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El IVA se causa cuando la contraprestación se cobra efectivamente (Art. 1-B y 17 LIVA), no al emitir la factura. En una operación PPD, el IVA del total facturado se reconoce conforme llegan los pagos, y el REP es el comprobante que lo ubica en cada periodo. Por eso una sola factura puede repartir su IVA en varios meses. En espejo, el receptor acredita ese IVA en el mes en que efectivamente paga (Art. 5, fracción III LIVA).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA POR PERIODO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importe cobrado (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA 16% (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Febrero 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(emisión, sin cobro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÓMO SE REGISTRA EN CADA PARTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emisor: IVA trasladado / a cargo (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receptor: IVA acreditable (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mismo importe por periodo; cambia el lado del registro: a cargo para quien cobra, acreditable para quien paga.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUADRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA reconocido en los pagos (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA de la factura de origen (MXN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamento: Arts. 1-B, 11 y 17 LIVA (causación del IVA por flujo de efectivo); Art. 5, fracción III LIVA (acreditamiento del IVA efectivamente pagado); Art. 32, fracción VIII LIVA (DIOT). El REP se rige por la regla 2.7.1.32 RMF.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,8 +445,15 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,6 +475,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF0FF"/>
+        <bgColor rgb="FFF4F8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -420,16 +534,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,19 +555,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -461,23 +579,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,44 +603,96 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -545,7 +715,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF1E7A1E"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -554,7 +724,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFF4F8FF"/>
       <rgbColor rgb="FFEAF0FF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -585,7 +755,7 @@
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF1E7A1E"/>
       <rgbColor rgb="FF0A1628"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -780,390 +950,390 @@
   <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>58000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="8" t="n">
         <f aca="false">ROUND(B9/1.16,2)</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <f aca="false">B9-B10</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="13" t="n">
         <f aca="false">B9</f>
         <v>58000</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="13" t="n">
         <f aca="false">G15-H15</f>
         <v>28000</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <f aca="false">ROUND(H15/1.16,2)</f>
         <v>25862.07</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="K15" s="13" t="n">
         <f aca="false">H15-J15</f>
         <v>4137.93</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="L15" s="15" t="n">
         <f aca="false">SUM($H$15:H15)/$B$9</f>
         <v>0.517241379310345</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="G16" s="13" t="n">
         <f aca="false">I15</f>
         <v>28000</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="14" t="n">
         <v>28000</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="13" t="n">
         <f aca="false">G16-H16</f>
         <v>0</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="J16" s="13" t="n">
         <f aca="false">ROUND(H16/1.16,2)</f>
         <v>24137.93</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">H16-J16</f>
         <v>3862.07</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="15" t="n">
         <f aca="false">SUM($H$15:H16)/$B$9</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16" t="n">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17" t="n">
         <f aca="false">SUM(H15:H16)</f>
         <v>58000</v>
       </c>
-      <c r="I17" s="16" t="n">
+      <c r="I17" s="17" t="n">
         <f aca="false">I16</f>
         <v>0</v>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="17" t="n">
         <f aca="false">SUM(J15:J16)</f>
         <v>50000</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="17" t="n">
         <f aca="false">SUM(K15:K16)</f>
         <v>8000</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="18" t="n">
         <f aca="false">H17/$B$9</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19" t="str">
+      <c r="B20" s="19"/>
+      <c r="C20" s="20" t="str">
         <f aca="false">IF(H17=B9,"✔ CUADRA","✘ REVISAR")</f>
         <v>✔ CUADRA</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19" t="str">
+      <c r="B21" s="19"/>
+      <c r="C21" s="20" t="str">
         <f aca="false">IF(I16=0,"✔ LIQUIDADA","✘ PENDIENTE")</f>
         <v>✔ LIQUIDADA</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19" t="str">
+      <c r="B22" s="19"/>
+      <c r="C22" s="20" t="str">
         <f aca="false">IF(K17=B11,"✔ CUADRA","✘ REVISAR")</f>
         <v>✔ CUADRA</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="13" t="n">
         <f aca="false">K15</f>
         <v>4137.93</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="13" t="n">
         <f aca="false">K16</f>
         <v>3862.07</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="16" t="n">
+      <c r="B28" s="23"/>
+      <c r="C28" s="17" t="n">
         <f aca="false">SUM(C26:C27)</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1194,124 +1364,563 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="24" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="B5" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="C5" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="31" t="n">
         <v>11600</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="G7" s="32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="35" t="n">
+        <f aca="false">'Análisis de Pagos'!B9</f>
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="35" t="n">
+        <f aca="false">'Análisis de Pagos'!B10</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="35" t="n">
+        <f aca="false">'Análisis de Pagos'!B11</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="D20" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!H15</f>
+        <v>30000</v>
+      </c>
+      <c r="E20" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!J15</f>
+        <v>25862.07</v>
+      </c>
+      <c r="F20" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!K15</f>
+        <v>4137.93</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>66</v>
-      </c>
+      <c r="D21" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!H16</f>
+        <v>28000</v>
+      </c>
+      <c r="E21" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!J16</f>
+        <v>24137.93</v>
+      </c>
+      <c r="F21" s="37" t="n">
+        <f aca="false">'Análisis de Pagos'!K16</f>
+        <v>3862.07</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="17" t="n">
+        <f aca="false">SUM(D19:D21)</f>
+        <v>58000</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <f aca="false">SUM(E19:E21)</f>
+        <v>50000</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <f aca="false">SUM(F19:F21)</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <f aca="false">F20</f>
+        <v>4137.93</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <f aca="false">F20</f>
+        <v>4137.93</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <f aca="false">F21</f>
+        <v>3862.07</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <f aca="false">F21</f>
+        <v>3862.07</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="17" t="n">
+        <f aca="false">SUM(B26:B27)</f>
+        <v>8000</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">SUM(C26:C27)</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="8" t="n">
+        <f aca="false">F22</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <f aca="false">B10</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="20" t="str">
+        <f aca="false">IF(F22=B10,"✔ CUADRA","✘ REVISAR")</f>
+        <v>✔ CUADRA</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A36:F37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
